--- a/results/run_complet_annee_dyn/metrics_rc.xlsx
+++ b/results/run_complet_annee_dyn/metrics_rc.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -580,6 +580,96 @@
         <v>0.03832460000012361</v>
       </c>
       <c r="M3" t="inlineStr">
+        <is>
+          <t>RC déroulement 24h</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0965302487931216</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.310693174680619</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1287823691000741</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.673440137164693</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.03374491652014354</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9903560567605914</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.4116381771955</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.09539152940217016</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3088551916386871</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0003435124707116941</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.3211982999964675</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>RC pas de temps 15min</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>11.49447360237228</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.390350070770315</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.57669699809264</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10.94543056085272</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-1.537715872631235</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.1483659513375064</v>
+      </c>
+      <c r="H5" t="n">
+        <v>15.40409633676895</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9.129903497430234</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.021573017060855</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0005667722478477212</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.2258153999973729</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>RC déroulement 24h</t>
         </is>
